--- a/plangec.xlsx
+++ b/plangec.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/j.cordry/lectures/gec/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{908DD767-7277-3A45-BBC1-3E76121A4935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0260E93C-AB80-2142-BDC9-F24864F74C0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="44800" windowHeight="24600" xr2:uid="{BE5DD1CB-FDE6-7646-99EA-B564C6016CF9}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="51">
   <si>
     <t>GPF</t>
   </si>
@@ -93,21 +93,12 @@
     <t>Lectures</t>
   </si>
   <si>
-    <t>Who</t>
-  </si>
-  <si>
     <t>Practical</t>
   </si>
   <si>
     <t>Notes</t>
   </si>
   <si>
-    <t>KD</t>
-  </si>
-  <si>
-    <t>IK</t>
-  </si>
-  <si>
     <t>No classes</t>
   </si>
   <si>
@@ -157,6 +148,51 @@
   </si>
   <si>
     <t>Jamie Matthews</t>
+  </si>
+  <si>
+    <t>Lecture 1</t>
+  </si>
+  <si>
+    <t>Lecture 2</t>
+  </si>
+  <si>
+    <t>Week 1 (Intro + SFML)</t>
+  </si>
+  <si>
+    <t>Week 2 (Structure + Animation)</t>
+  </si>
+  <si>
+    <t>Week 3 (Simulation + Collisions)</t>
+  </si>
+  <si>
+    <t>Week 4 (Vectors + ECS)</t>
+  </si>
+  <si>
+    <t>Week 5 (Pixel Perfect)</t>
+  </si>
+  <si>
+    <t>Week 6 (Virtual Worlds)</t>
+  </si>
+  <si>
+    <t>Week 7 (ICA + Virtual Worlds Cont.)</t>
+  </si>
+  <si>
+    <t>Week 8 </t>
+  </si>
+  <si>
+    <t>Animex</t>
+  </si>
+  <si>
+    <t>Week 9 (Physics)</t>
+  </si>
+  <si>
+    <t>Week 10 (Sound, AI + Additional ICA info)</t>
+  </si>
+  <si>
+    <t>Week 11 (Patterns)</t>
+  </si>
+  <si>
+    <t>Week 12 (Final Issues)</t>
   </si>
 </sst>
 </file>
@@ -534,209 +570,309 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28437098-5992-EB44-B125-87EAF2925C29}">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="26.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.1640625" customWidth="1"/>
+    <col min="4" max="4" width="14.1640625" customWidth="1"/>
+    <col min="5" max="5" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>16</v>
       </c>
       <c r="C2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" t="s">
         <v>17</v>
       </c>
-      <c r="D2" t="s">
+      <c r="G2" t="s">
         <v>18</v>
       </c>
-      <c r="F2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+      <c r="D4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+      <c r="D5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
         <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+      <c r="D10" t="s">
+        <v>46</v>
+      </c>
+      <c r="G10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+      <c r="D11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" t="s">
         <v>20</v>
       </c>
-      <c r="D13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="E14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C17" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D17">
-        <f>COUNTIF(C3:C14,C17)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.2">
+        <f>COUNTIF(C$3:C$14,C17)+COUNTIF(D$3:D$14,C17)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C18" t="s">
         <v>13</v>
       </c>
       <c r="D18">
-        <f>COUNTIF(C3:C14,C18)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.2">
+        <f>COUNTIF(C$3:C$14,C18)+COUNTIF(D$3:D$14,C18)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C19" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D19">
-        <f>COUNTIF(C3:C14,C19)</f>
-        <v>1</v>
+        <f>COUNTIF(C$3:C$14,C19)+COUNTIF(D$3:D$14,C19)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
